--- a/Result/profitability/2365.xlsx
+++ b/Result/profitability/2365.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2025</v>
+        <v>0.19</v>
       </c>
       <c r="N2" t="n">
-        <v>38.1225</v>
+        <v>37.7225</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0.255</v>
+        <v>0.25875</v>
       </c>
       <c r="N3" t="n">
-        <v>35.4325</v>
+        <v>35.335</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.34</v>
       </c>
       <c r="M4" t="n">
-        <v>0.41125</v>
+        <v>0.4175</v>
       </c>
       <c r="N4" t="n">
-        <v>33.3025</v>
+        <v>33.2525</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.26</v>
       </c>
       <c r="M5" t="n">
-        <v>0.435</v>
+        <v>0.455</v>
       </c>
       <c r="N5" t="n">
-        <v>30.94125</v>
+        <v>30.3075</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.64</v>
       </c>
       <c r="M6" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="N6" t="n">
-        <v>28.31375</v>
+        <v>27.9075</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.46</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5525</v>
+        <v>0.555</v>
       </c>
       <c r="N7" t="n">
-        <v>25.52125</v>
+        <v>25.34</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.78</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6375000000000001</v>
+        <v>0.635</v>
       </c>
       <c r="N8" t="n">
-        <v>22.89375</v>
+        <v>22.79125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.64</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>20.19125</v>
@@ -1772,7 +1772,7 @@
         <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6325000000000001</v>
+        <v>0.6325</v>
       </c>
       <c r="N11" t="n">
         <v>19.95375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2365</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>247</v>
+      </c>
+      <c r="D75" t="n">
+        <v>152</v>
+      </c>
+      <c r="E75" t="n">
+        <v>95</v>
+      </c>
+      <c r="F75" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="G75" t="n">
+        <v>9</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>3.68%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>20</v>
+      </c>
+      <c r="J75" t="n">
+        <v>29</v>
+      </c>
+      <c r="K75" t="n">
+        <v>26</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.1125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.31125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.142857142857143</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8200000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.02088639836984207</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1165249367961388</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
